--- a/plots/sample_table.xlsx
+++ b/plots/sample_table.xlsx
@@ -14,7 +14,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
-    <t>COMMON_NAME</t>
+    <t>common_name</t>
   </si>
   <si>
     <t>YEAR</t>
@@ -41,52 +41,52 @@
     <t>walleye pollock</t>
   </si>
   <si>
-    <t>66.1 (39.0-98.0)</t>
-  </si>
-  <si>
-    <t>71.9 (53.0-101.0)</t>
-  </si>
-  <si>
-    <t>51.0 (40.0-65.0)</t>
-  </si>
-  <si>
-    <t>57.3 (50.0-66.0)</t>
-  </si>
-  <si>
-    <t>3.82 (0.62-12.32)</t>
+    <t>67.0 (44.0-95.0)</t>
+  </si>
+  <si>
+    <t>72.2 (53.0-101.0)</t>
+  </si>
+  <si>
+    <t>50.6 (40.0-65.0)</t>
+  </si>
+  <si>
+    <t>56.9 (50.0-66.0)</t>
+  </si>
+  <si>
+    <t>3.98 (0.92-10.81)</t>
   </si>
   <si>
     <t>4.86 (1.74-13.55)</t>
   </si>
   <si>
-    <t>0.89 (0.43-1.95)</t>
-  </si>
-  <si>
-    <t>1.18 (0.76-1.73)</t>
-  </si>
-  <si>
-    <t>5.4 (3.0-9.0)</t>
+    <t>0.86 (0.43-1.95)</t>
+  </si>
+  <si>
+    <t>1.17 (0.76-1.73)</t>
+  </si>
+  <si>
+    <t>5.4 (3.0-8.0)</t>
   </si>
   <si>
     <t>5.5 (3.0-9.0)</t>
   </si>
   <si>
-    <t>7.5 (3.0-13.0)</t>
+    <t>7.4 (3.0-13.0)</t>
   </si>
   <si>
     <t>9.7 (6.0-13.0)</t>
   </si>
   <si>
-    <t>144.7 (5.0-800.0)</t>
+    <t>152.7 (20.0-595.0)</t>
   </si>
   <si>
     <t>214.8 (35.0-820.0)</t>
   </si>
   <si>
-    <t>50.6 (18.0-140.0)</t>
-  </si>
-  <si>
-    <t>52.1 (15.0-100.0)</t>
+    <t>49.7 (20.0-140.0)</t>
+  </si>
+  <si>
+    <t>52.5 (15.0-100.0)</t>
   </si>
 </sst>
 </file>
@@ -165,7 +165,7 @@
         <v>2021.0</v>
       </c>
       <c r="C2" t="n">
-        <v>67.0</v>
+        <v>42.0</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -211,7 +211,7 @@
         <v>2021.0</v>
       </c>
       <c r="C4" t="n">
-        <v>60.0</v>
+        <v>49.0</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -234,7 +234,7 @@
         <v>2022.0</v>
       </c>
       <c r="C5" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
